--- a/Results/Two_Datasets_Assessment/Mushroom/Tables/privacy_scores.xlsx
+++ b/Results/Two_Datasets_Assessment/Mushroom/Tables/privacy_scores.xlsx
@@ -478,13 +478,13 @@
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>0.5965175288041394</v>
+        <v>0.5651465293055633</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2422318876841711</v>
+        <v>0.3057528156749705</v>
       </c>
       <c r="G2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3">
@@ -505,13 +505,13 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>0.5898036904498916</v>
+        <v>0.6793990320601035</v>
       </c>
       <c r="F3" t="n">
-        <v>0.3382438588682164</v>
+        <v>0.3920273153705516</v>
       </c>
       <c r="G3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4">
@@ -532,13 +532,13 @@
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>0.425874725649952</v>
+        <v>0.580711160887031</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4421103533686161</v>
+        <v>0.4742130076258645</v>
       </c>
       <c r="G4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5">
@@ -559,13 +559,13 @@
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>0.8740643163992137</v>
+        <v>0.6501790175485291</v>
       </c>
       <c r="F5" t="n">
-        <v>0.2181270024824805</v>
+        <v>0.3697767981582697</v>
       </c>
       <c r="G5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6">
@@ -586,13 +586,13 @@
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>0.4949530413496791</v>
+        <v>0.542977064252405</v>
       </c>
       <c r="F6" t="n">
-        <v>0.414551150728962</v>
+        <v>0.4540085148638113</v>
       </c>
       <c r="G6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7">
@@ -613,13 +613,13 @@
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>0.6238393249874938</v>
+        <v>0.7325289107288828</v>
       </c>
       <c r="F7" t="n">
-        <v>0.3788110168065982</v>
+        <v>0.3846235259007812</v>
       </c>
       <c r="G7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8">
@@ -640,13 +640,13 @@
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>0.25</v>
+        <v>0.2294567983077689</v>
       </c>
       <c r="F8" t="n">
-        <v>0.4330127018922193</v>
+        <v>0.37104157201863</v>
       </c>
       <c r="G8" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9">
@@ -667,13 +667,13 @@
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>0.5520664642022749</v>
+        <v>0.5187481196936311</v>
       </c>
       <c r="F9" t="n">
-        <v>0.2518670578036035</v>
+        <v>0.3424820228872009</v>
       </c>
       <c r="G9" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
